--- a/labeling/data/avito_product_analyst_middle_20240404.splitter.v1.mock.xlsx
+++ b/labeling/data/avito_product_analyst_middle_20240404.splitter.v1.mock.xlsx
@@ -515,6 +515,16 @@
           <t>00:07:50</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>- это софт скилы вот тоже тут коротко пройдусь а ну SQL у меня был опыт с Клик хаусом Веркой mysql pog и py Ну естественно работал с оконными функциями вот далее Pon - это тоже стандартный такой набор пан па в принципе тут всё перечислено вот Аа ну и а тесты статистика а плюс визуализация в супер сайте в табло это тоже то с чем я работал Ну ещё тоже интересные такие навыки которые я сюда добавил это презентация результатов и интерес к Великому тоже Ну интерес к Великому Я здесь подразумеваю там критическое мышление и вот какие-то такие вопросы а почему а зачем вот а и переходим к софт скилам это ответственность и самостоятельность После перехода там на уровень мил и выше естественно такое такие навыки должны преобладать у аналитика вот выстраивание процессов работы команды это там планирование команды обучение - это всё мой опыт менеджер Вот про активный подход к аналитике коммуникабельность и вот про управлени командой Я тоже поговорил Это как в рабочее время так и в нерабочее время Угу Да здорово А в принципе в моём плане</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>00:10:38</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>hard</t>
@@ -619,6 +629,16 @@
           <t>00:14:28</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>план запроса смотрел Ну использовал вообще этот инструмент м план запроса но Джов например шесть джоновна сделать А и кстати тоже небольшой втоп я сам даже проводил такое тестирование gpt 3,5 и чет версии четвёртая версия лучше справляется с круто окей да спасибо спасибо что поделился и про pyon Скажи пожалуйста ну</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>00:14:20</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>hard</t>
@@ -723,6 +743,16 @@
           <t>00:17:12</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>поделился давай двигаться дальше тогда Угу спасибо за вопросы так Ну тут у меня уже идёт Да блог с какими-то моими кейсами с результатами точнее даже А во время предыдущих работ и на текущем месте работы вот здесь просто наверно коротко скажу как я обычно рассказываю Вот и дальше наверное можем уже твоим вопросом по этой части перейти То есть я придерживаюсь следующей структуры что у меня есть результат Ну вот берём намер слева а by clients вот есть результаты и дальше Вот четыре блока четыре пункта - это сама ситуация то есть погрузиться немного в контекст чтобы ну ты как менеджер тоже понимал вот дальше это сама задача что из себя представляла В каком виде там она ко мне пришла Вот что делал и ну результат уже да как таковой он тут присутствует вот Так у меня расписаны как раз все мои кейсы в таком ключе Ну естественно в самом результате важно метри результат делать Вот чтобы понимать к чему какому результату мы пришли вот да у меня тут расписано [музыка]</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>00:17:57</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>hard</t>
@@ -827,6 +857,16 @@
           <t>00:26:48</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>потратить чуть больше времени Вот потому что эффект интересный может быть какая-то другая сегментация нам может показать Ну не знаю инсайты Угу угу окей да спасибо спасибо что поделился а сжи пожалуйста вот прок Э ты говоришь что там 2/3 задач появляются из твоего бэклога а формулируется формируется он кем то есть это что-то уже изначально давно было и вы разгребает его или вы Пополняется его пополняет его продуктами аналитиками то есть вообще как как он как он какой жизне он живёт э клока ну базово он от продукта идёт Угу То есть он как раз-таки к планированию Да всё это собирает но в этом планировании также участвуем Discovery команда я вот ну совместно с продуктом Ну ещё кстати технический менеджер тоже техлит включается Вот и мы уже и со своей стороны тоже можем какие-то свои идеи мысли вот я не знаю с предыдущих ресей набрасывать Вот Ну а я со своей стороны там когда мы обсуждаем идеи Стараюсь больше как-то аналитически ну то есть какие-то данные сюда подкидывать чтобы мы не просто там потому что нам так кажется у конкурентов так есть вот но ещё и наш бизнесом наших пользователей окей да</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>00:27:10</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>hard</t>
@@ -874,6 +914,16 @@
           <t>00:29:00</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>р там со своей стороны Ну я вот стараюсь если у нас есть гипотеза Ну или фича не знають в этом квартале задаю вопрос всегда А почему мы решили что это поможет а какие проблемы это решает А ну в общем Откуда это появилось что мы поможем как мы поможем пользователям нашим вот ну и есть ли какие-то данные То есть просто на словах сказать что там решим вот такую-то проблему вот в разных случаях данные тоже могут быть Да и получается что вот э эти задачи ты как раз в квартальном планировани приносишь да Или это в операционки ты как бы там условно каждый спринт можешь придумать что-то принести и сделать То есть м ну операционка - это с моей стороны Да А мы на квартал планируем если ресерч то тут Наверное чаще всего это да мы вот планируем на квартал но если я во время не знаю подведение результатов об обнаружил какие-то не знаю разные инсайты о которых мы Ну просто думали не видели то тоже можно чуть в другую сторону погрузиться А ну это наверное тоже если в процентном соотношении там не знаю 80 на 20 где-то вот прямо льно новая задача может появиться О'кей понятно да спасибо</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>00:30:47</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>hard</t>
@@ -921,6 +971,16 @@
           <t>00:32:56</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>вот зоне нте там вот не знаю ли с первого дня что ли взаимодействие была куча заказчиков и нужно было да научиться говорить нет Ладно сейчас Лирику уберём как я разруливает забираю там Почему эта задача важна что это даст бизнесу Угу а какие-то внешние дедлайны То есть это не просто не знаю Мне нужно через неделю А может быть это связано там со встречей с топ менеджментом там ещё связано то есть вот какие-то такие внешние дедлайны которые тоже влияют угу вот а это Ключевое М сейчас ну дальше Да мне нужно от приоритизировать со своей стороны там накинуть приоритеты исходя там из и времени выполнения задач тоже прикинуть пример там не знаю условный гант вот как как это всё ну и периодически тоже бывает что нужно до уточнять что-то Чтобы понимать больше контекста и оценить вот Ну наверно тоже в Дета могу приме Я в целом Я в целом понял про Ну некоторую такую скоринг задач и там по их важности ценности там</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>00:33:04</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>hard</t>
@@ -968,6 +1028,16 @@
           <t>00:34:54</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>срочности и так далее анально решение принимаешь сам условно что взять А что не взять или это как-то дальше возвращаешь заказчикам говоришь Ребят вы вы не важны там сейчас условно Да ваша задача там стоит меньше чем задача ваших коллег Да конечно скрипя не знаю на серд со скрипом сердце приходится отказывать но все все люди понимающие Вот и когда я просто объясняю не просто говорю что нет мы не берём задачу всё Угу они просто уходят А я естественно прихожу с каким-то доводами Почему я не могу есть другие задачи и Ну да есть другие задачи Угу Вот они более ценные важные Вот и если как бы заказчик О'кей он понимает Угу мои доводы то тут точка Если не окей то нужно идти уже чуть выше там чаще всего это руководители как раз эти заказчиков менеджеров в моём последнем случае вот у них которым я уже обсуждаю вот полу задач Как ты считаешь и почему Понятно СБО скажи поста тогда такой вот небольшой дида сделаем в сторону твоих задач и попрошу тебя рассказать</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>00:34:34</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>hard</t>
@@ -1194,6 +1264,16 @@
       <c r="F15" t="inlineStr">
         <is>
           <t>00:57:56</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ориентируемся на Ну не только на Telegram Вот потому что - это именно вот коммуникация там я не знаю в повседневной жизни в более общих что ли точнее в разных кейсах вот не как у нас но Так что что ж мне такого не хватает а может быть взять из каких-то других продуктов э не знаю пусть будет я вот кстати не помню не встречался а не встречался короче переводчик например Да например я переписываюсь там с разными людьми на разном языке на на разных языках не только вот и там я не знаю Мне нужен Ну с английским ещё более-менее вот какие-то другие например языки то есть взял перевод включил Я единственное знаю что по-моему в каналах или в чатах при каналах я могу по-моему в каналах типа нажать на кнопочку translate английский точно есть возможно други тоже есть но типа в обычных по-моему переписках я например в личке с кем-то перепис такого вроде нет Угу И было бы как раз-таки удобно Я не знаю какой-нибудь продвинутый уже переводчик Google dipel что-нибудь такое вот наверно мне сейчас в голову пришло А давай смотри Давай представим</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>00:57:41</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
